--- a/wedding_forms/041_wedding_videography_request_form--wedding_forms.xlsx
+++ b/wedding_forms/041_wedding_videography_request_form--wedding_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1114,8 +1114,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'option_2':_'option_2'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'option_2': 'Option 2'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1160,12 +1160,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'option_3':_'option_3'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'option_3': 'Option 3'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1177,12 +1177,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'option_4':_'option_4'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'option_4': 'Option 4'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1194,12 +1194,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'option_5':_'option_5'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'option_5': 'Option 5'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1211,12 +1211,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'option_6':_'option_6'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'option_6': 'Option 6'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'option_7':_'option_7'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'option_7': 'Option 7'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1245,12 +1245,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'option_8':_'package_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'option_8': 'Package 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1262,12 +1262,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'option_9':_'package_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'option_9': 'Package 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1279,12 +1279,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'option_10':_'package_3'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'option_10': 'Package 3'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1296,12 +1296,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'option_11':_'add-on_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'option_11': 'Add-on 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1313,12 +1313,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'option_12':_'add-on_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'option_12': 'Add-on 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1330,12 +1330,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'option_13':_'add-on_3'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'option_13': 'Add-on 3'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'option_14':_'add-on_4'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'option_14': 'Add-on 4'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1364,12 +1364,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'option_15':_'add-on_5'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'option_15': 'Add-on 5'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1381,12 +1381,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'option_16':_'add-on_6'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'option_16': 'Add-on 6'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1398,12 +1398,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'option_17':_'add-on_7'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'option_17': 'Add-on 7'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'option_18':_'add-on_8'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'option_18': 'Add-on 8'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1432,12 +1432,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'option_19':_'add-on_9'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'option_19': 'Add-on 9'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1449,12 +1449,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'option_20':_'add-on_10'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'option_20': 'Add-on 10'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'option_21':_'add-on_11'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'option_21': 'Add-on 11'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1483,12 +1483,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'option_22':_'add-on_12'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'option_22': 'Add-on 12'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1500,12 +1500,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'option_23':_'add-on_13'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'option_23': 'Add-on 13'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1517,12 +1517,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'option_24':_'add-on_14'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'option_24': 'Add-on 14'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1534,12 +1534,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'option_25':_'add-on_15'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'option_25': 'Add-on 15'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1551,12 +1551,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'option_26':_'add-on_16'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'option_26': 'Add-on 16'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1568,12 +1568,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'option_27':_'add-on_17'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'option_27': 'Add-on 17'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'option_28':_'add-on_18'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'option_28': 'Add-on 18'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
